--- a/data/trans_orig/P35-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007 (tasa de respuesta: 95,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65978</t>
+          <t>64823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97684</t>
+          <t>97753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>37546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109228</t>
+          <t>108272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153841</t>
+          <t>148872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357210</t>
+          <t>357141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388916</t>
+          <t>390071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231086</t>
+          <t>231663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257648</t>
+          <t>256664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595263</t>
+          <t>600232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>639876</t>
+          <t>640832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>53594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84484</t>
+          <t>84424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66583</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99934</t>
+          <t>99785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141398</t>
+          <t>138902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293109</t>
+          <t>294246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276910</t>
+          <t>276940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303782</t>
+          <t>305819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549935</t>
+          <t>552431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>591399</t>
+          <t>591548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87438</t>
+          <t>88739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124596</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>45267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120772</t>
+          <t>119667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>160178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>391331</t>
+          <t>390605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428489</t>
+          <t>427188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115989</t>
+          <t>116522</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137375</t>
+          <t>137595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>517539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556945</t>
+          <t>558050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210453</t>
+          <t>210751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265884</t>
+          <t>262853</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117989</t>
+          <t>116040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156727</t>
+          <t>156715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340100</t>
+          <t>340899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407432</t>
+          <t>408742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916870</t>
+          <t>919901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>972301</t>
+          <t>972003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522628</t>
+          <t>522640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>561366</t>
+          <t>563315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1454677</t>
+          <t>1453367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1522009</t>
+          <t>1521210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>51504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>77030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>113976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111995</t>
+          <t>112271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154821</t>
+          <t>156009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280648</t>
+          <t>280914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304058</t>
+          <t>304656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>426013</t>
+          <t>424131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>460800</t>
+          <t>461077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>715704</t>
+          <t>714516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>758530</t>
+          <t>758254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>292952</t>
+          <t>297968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>357503</t>
+          <t>360791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>313629</t>
+          <t>314912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>376907</t>
+          <t>379032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258960</t>
+          <t>261151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276321</t>
+          <t>276898</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>832503</t>
+          <t>829215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>897054</t>
+          <t>892038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1100135</t>
+          <t>1098010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1163413</t>
+          <t>1162130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>504178</t>
+          <t>511424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>587330</t>
+          <t>593110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>648121</t>
+          <t>646001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>742525</t>
+          <t>742347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1179381</t>
+          <t>1179322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1312317</t>
+          <t>1304734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2533539</t>
+          <t>2527759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2616691</t>
+          <t>2609445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2464435</t>
+          <t>2464613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2558839</t>
+          <t>2560959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5015512</t>
+          <t>5023095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5148448</t>
+          <t>5148507</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012 (tasa de respuesta: 97,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93285</t>
+          <t>93943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133708</t>
+          <t>133323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>101646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174983</t>
+          <t>173290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225608</t>
+          <t>225131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293726</t>
+          <t>294111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334149</t>
+          <t>333491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200029</t>
+          <t>202693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233464</t>
+          <t>234605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506165</t>
+          <t>506642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556790</t>
+          <t>558483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89202</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127435</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>82308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>118420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179737</t>
+          <t>179205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233873</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276182</t>
+          <t>276529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314415</t>
+          <t>317284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209969</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246989</t>
+          <t>246841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>498893</t>
+          <t>499616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>553029</t>
+          <t>553561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153848</t>
+          <t>152903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201203</t>
+          <t>199217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>76836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108356</t>
+          <t>108199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241224</t>
+          <t>239875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293888</t>
+          <t>296019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405658</t>
+          <t>407644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453013</t>
+          <t>453958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147610</t>
+          <t>147767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178817</t>
+          <t>179130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568939</t>
+          <t>566808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621603</t>
+          <t>622952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294141</t>
+          <t>294322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>355829</t>
+          <t>357980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208601</t>
+          <t>206922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259264</t>
+          <t>260558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>514670</t>
+          <t>518594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601308</t>
+          <t>601865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>769996</t>
+          <t>767845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831684</t>
+          <t>831503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483224</t>
+          <t>481930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>533887</t>
+          <t>535566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267004</t>
+          <t>1266447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1353642</t>
+          <t>1349718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>109488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151446</t>
+          <t>151498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221647</t>
+          <t>222556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276992</t>
+          <t>273562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347403</t>
+          <t>345994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414302</t>
+          <t>415067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>353288</t>
+          <t>353236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393255</t>
+          <t>395246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461822</t>
+          <t>465252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>517167</t>
+          <t>516258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>829246</t>
+          <t>828481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>896145</t>
+          <t>897554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>23706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>388375</t>
+          <t>389262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>455042</t>
+          <t>454912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>402339</t>
+          <t>401252</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>471833</t>
+          <t>470442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230276</t>
+          <t>230488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245229</t>
+          <t>245715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>619157</t>
+          <t>619287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>685824</t>
+          <t>684937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>856561</t>
+          <t>857952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>926055</t>
+          <t>927142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>808004</t>
+          <t>811307</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>917677</t>
+          <t>912489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1123125</t>
+          <t>1130354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1240312</t>
+          <t>1242727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1971456</t>
+          <t>1970646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2126668</t>
+          <t>2125479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2404988</t>
+          <t>2410176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2514661</t>
+          <t>2511358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2204643</t>
+          <t>2202228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2321830</t>
+          <t>2314601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4640952</t>
+          <t>4642141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4796164</t>
+          <t>4796974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016 (tasa de respuesta: 98,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111113</t>
+          <t>109100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>148937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>85031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117693</t>
+          <t>118489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203370</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257332</t>
+          <t>256355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270991</t>
+          <t>274564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312388</t>
+          <t>314401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226297</t>
+          <t>225501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260650</t>
+          <t>258959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510159</t>
+          <t>511136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>564121</t>
+          <t>563953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85221</t>
+          <t>86598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120801</t>
+          <t>120230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>95063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>131531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191789</t>
+          <t>188638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241931</t>
+          <t>241427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247907</t>
+          <t>248478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283487</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233620</t>
+          <t>234473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>270883</t>
+          <t>270941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492781</t>
+          <t>493285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>542923</t>
+          <t>546074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144640</t>
+          <t>141552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188425</t>
+          <t>185900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72675</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200831</t>
+          <t>199529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250282</t>
+          <t>248547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325243</t>
+          <t>327768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>369028</t>
+          <t>372116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>91193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116990</t>
+          <t>116503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427512</t>
+          <t>429247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476963</t>
+          <t>478265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>296255</t>
+          <t>297148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>357204</t>
+          <t>360695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231635</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287645</t>
+          <t>284159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>542204</t>
+          <t>544747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>630808</t>
+          <t>630060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>780864</t>
+          <t>777373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841813</t>
+          <t>840920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>526830</t>
+          <t>530316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582840</t>
+          <t>582415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1321735</t>
+          <t>1322483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410339</t>
+          <t>1407796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151664</t>
+          <t>152593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195998</t>
+          <t>195855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283410</t>
+          <t>281688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339147</t>
+          <t>337699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>446809</t>
+          <t>443735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>522292</t>
+          <t>517273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412754</t>
+          <t>412897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457088</t>
+          <t>456159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393200</t>
+          <t>394648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>448937</t>
+          <t>450659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>818807</t>
+          <t>823826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894290</t>
+          <t>897364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>342803</t>
+          <t>341302</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>405249</t>
+          <t>405731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>369218</t>
+          <t>367350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>440437</t>
+          <t>441354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236863</t>
+          <t>238401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258426</t>
+          <t>259275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>659076</t>
+          <t>658594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>721522</t>
+          <t>723023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>902084</t>
+          <t>901167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973303</t>
+          <t>975171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>876881</t>
+          <t>876675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>980970</t>
+          <t>980787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1157198</t>
+          <t>1154800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1276417</t>
+          <t>1271970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2065070</t>
+          <t>2056017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2229699</t>
+          <t>2216051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2349922</t>
+          <t>2350105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2454011</t>
+          <t>2454217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2208850</t>
+          <t>2213297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2328069</t>
+          <t>2330467</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4586460</t>
+          <t>4600108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4751089</t>
+          <t>4760142</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>152856</t>
+          <t>150701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194864</t>
+          <t>194761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109069</t>
+          <t>111115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140673</t>
+          <t>140402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272003</t>
+          <t>270124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325483</t>
+          <t>324051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310348</t>
+          <t>310451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>352356</t>
+          <t>354511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306794</t>
+          <t>307065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338398</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627196</t>
+          <t>628628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>680676</t>
+          <t>682555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153948</t>
+          <t>153453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196782</t>
+          <t>194822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128650</t>
+          <t>126255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160259</t>
+          <t>159179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>291356</t>
+          <t>294288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342435</t>
+          <t>346434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255431</t>
+          <t>257391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298265</t>
+          <t>298760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221490</t>
+          <t>222570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253099</t>
+          <t>255494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>491526</t>
+          <t>487527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>542605</t>
+          <t>539673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61597</t>
+          <t>61303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269162</t>
+          <t>269612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80185</t>
+          <t>80147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97950</t>
+          <t>114661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340386</t>
+          <t>337698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399102</t>
+          <t>398652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606667</t>
+          <t>606961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86726</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107508</t>
+          <t>107861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494789</t>
+          <t>497477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>737225</t>
+          <t>720514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339022</t>
+          <t>337054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>407220</t>
+          <t>404689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133284</t>
+          <t>118993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>328390</t>
+          <t>326914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>421350</t>
+          <t>437775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>707722</t>
+          <t>710019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627599</t>
+          <t>630130</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>695797</t>
+          <t>697765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648166</t>
+          <t>649642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>843272</t>
+          <t>857563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1303653</t>
+          <t>1301356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1590025</t>
+          <t>1573600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131005</t>
+          <t>133868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174769</t>
+          <t>173740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239691</t>
+          <t>257419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>384846</t>
+          <t>390498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>404796</t>
+          <t>394802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537966</t>
+          <t>538433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>341178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454150</t>
+          <t>448498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>599305</t>
+          <t>581577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>776075</t>
+          <t>775608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909245</t>
+          <t>919239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>289659</t>
+          <t>290020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341173</t>
+          <t>341335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>323408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>389111</t>
+          <t>389168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177943</t>
+          <t>177405</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>213838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>419251</t>
+          <t>419089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>470765</t>
+          <t>470404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>611820</t>
+          <t>611763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>673992</t>
+          <t>677523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>816632</t>
+          <t>841527</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1179208</t>
+          <t>1181047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1004297</t>
+          <t>1016340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1357447</t>
+          <t>1353526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2018866</t>
+          <t>2019848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2485436</t>
+          <t>2490818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2196852</t>
+          <t>2195013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2559428</t>
+          <t>2534533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2214655</t>
+          <t>2218576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2567805</t>
+          <t>2555762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4462727</t>
+          <t>4457345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4929297</t>
+          <t>4928315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64823</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97753</t>
+          <t>99924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37546</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62547</t>
+          <t>62999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108272</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148872</t>
+          <t>151026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357141</t>
+          <t>354970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390071</t>
+          <t>388842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231663</t>
+          <t>231211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>258126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>600232</t>
+          <t>598078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>640832</t>
+          <t>639419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53594</t>
+          <t>54853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84424</t>
+          <t>84432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66553</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99785</t>
+          <t>100258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138902</t>
+          <t>141435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263416</t>
+          <t>263408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294246</t>
+          <t>292987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276940</t>
+          <t>277957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305819</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>552431</t>
+          <t>549898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>591548</t>
+          <t>591075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88739</t>
+          <t>88712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125322</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>46627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119667</t>
+          <t>120544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160178</t>
+          <t>163984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390605</t>
+          <t>389088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427188</t>
+          <t>427215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116522</t>
+          <t>115162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137595</t>
+          <t>137333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517539</t>
+          <t>513733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558050</t>
+          <t>557173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210751</t>
+          <t>211880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262853</t>
+          <t>264518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116040</t>
+          <t>116005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156715</t>
+          <t>157929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340899</t>
+          <t>338766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408742</t>
+          <t>405816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919901</t>
+          <t>918236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>972003</t>
+          <t>970874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522640</t>
+          <t>521426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>563315</t>
+          <t>563350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1453367</t>
+          <t>1456293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1521210</t>
+          <t>1523343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51504</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77030</t>
+          <t>76750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113976</t>
+          <t>113250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112271</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156009</t>
+          <t>153453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280914</t>
+          <t>282986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304656</t>
+          <t>306186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424131</t>
+          <t>424857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461077</t>
+          <t>461357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>714516</t>
+          <t>717072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>758254</t>
+          <t>760394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>297968</t>
+          <t>300568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>360791</t>
+          <t>360883</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>314912</t>
+          <t>312519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>379032</t>
+          <t>376370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261151</t>
+          <t>261204</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276898</t>
+          <t>277042</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>829215</t>
+          <t>829123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>892038</t>
+          <t>889438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1098010</t>
+          <t>1100672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1162130</t>
+          <t>1164523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>511424</t>
+          <t>506361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593110</t>
+          <t>590009</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>646001</t>
+          <t>647800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>742347</t>
+          <t>741561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1179322</t>
+          <t>1179402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1304734</t>
+          <t>1302498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2527759</t>
+          <t>2530860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2609445</t>
+          <t>2614508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2464613</t>
+          <t>2465399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2560959</t>
+          <t>2559160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5023095</t>
+          <t>5025331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5148507</t>
+          <t>5148427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>91052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133323</t>
+          <t>133421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69734</t>
+          <t>71021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101646</t>
+          <t>104846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173290</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225131</t>
+          <t>222117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294111</t>
+          <t>294013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>333491</t>
+          <t>336382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202693</t>
+          <t>199493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234605</t>
+          <t>233318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506642</t>
+          <t>509656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>558483</t>
+          <t>559522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86333</t>
+          <t>87278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127088</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82308</t>
+          <t>83806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118420</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179205</t>
+          <t>180027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233150</t>
+          <t>231076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276529</t>
+          <t>277669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317284</t>
+          <t>316339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210729</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246841</t>
+          <t>245343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499616</t>
+          <t>501690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>553561</t>
+          <t>552739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152903</t>
+          <t>153229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199217</t>
+          <t>199904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76836</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108199</t>
+          <t>108767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239875</t>
+          <t>242436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296019</t>
+          <t>298561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407644</t>
+          <t>406957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453958</t>
+          <t>453632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147767</t>
+          <t>147199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179130</t>
+          <t>177858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>566808</t>
+          <t>564266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622952</t>
+          <t>620391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294322</t>
+          <t>291758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>357980</t>
+          <t>357102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206922</t>
+          <t>210332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260558</t>
+          <t>262241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>518594</t>
+          <t>516197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601865</t>
+          <t>601927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>767845</t>
+          <t>768723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831503</t>
+          <t>834067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481930</t>
+          <t>480247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>535566</t>
+          <t>532156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266447</t>
+          <t>1266385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1349718</t>
+          <t>1352115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109488</t>
+          <t>110285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151498</t>
+          <t>150839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222556</t>
+          <t>223995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>273562</t>
+          <t>275300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345994</t>
+          <t>350339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415067</t>
+          <t>412902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>353236</t>
+          <t>353895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395246</t>
+          <t>394449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465252</t>
+          <t>463514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516258</t>
+          <t>514819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>828481</t>
+          <t>830646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>897554</t>
+          <t>893209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>389262</t>
+          <t>389681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>454912</t>
+          <t>456990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>401252</t>
+          <t>401237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>470442</t>
+          <t>473918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230488</t>
+          <t>230511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245715</t>
+          <t>245213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>619287</t>
+          <t>617209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>684937</t>
+          <t>684518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>857952</t>
+          <t>854476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>927142</t>
+          <t>927157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>811307</t>
+          <t>810276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>912489</t>
+          <t>915555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1130354</t>
+          <t>1121727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1242727</t>
+          <t>1237921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1970646</t>
+          <t>1964633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2125479</t>
+          <t>2127692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2410176</t>
+          <t>2407110</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2511358</t>
+          <t>2512389</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2202228</t>
+          <t>2207034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2314601</t>
+          <t>2323228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4642141</t>
+          <t>4639928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4796974</t>
+          <t>4802987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109100</t>
+          <t>110918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148937</t>
+          <t>150326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85031</t>
+          <t>83890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118489</t>
+          <t>118723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203538</t>
+          <t>205118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256355</t>
+          <t>259739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274564</t>
+          <t>273175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314401</t>
+          <t>312583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225501</t>
+          <t>225267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258959</t>
+          <t>260100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511136</t>
+          <t>507752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563953</t>
+          <t>562373</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86598</t>
+          <t>86753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120230</t>
+          <t>121473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>96605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131531</t>
+          <t>132210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188638</t>
+          <t>192268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241427</t>
+          <t>240094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248478</t>
+          <t>247235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>281955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234473</t>
+          <t>233794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>270941</t>
+          <t>269399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>493285</t>
+          <t>494618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>546074</t>
+          <t>542444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141552</t>
+          <t>143655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185900</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72933</t>
+          <t>72239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199529</t>
+          <t>200579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248547</t>
+          <t>251098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327768</t>
+          <t>328785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372116</t>
+          <t>370013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91193</t>
+          <t>91887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116503</t>
+          <t>117116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>429247</t>
+          <t>426696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>478265</t>
+          <t>477215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>297148</t>
+          <t>295786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360695</t>
+          <t>358249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>232060</t>
+          <t>233586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284159</t>
+          <t>286112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>544747</t>
+          <t>547009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>630060</t>
+          <t>626984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>777373</t>
+          <t>779819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>840920</t>
+          <t>842282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530316</t>
+          <t>528363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582415</t>
+          <t>580889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322483</t>
+          <t>1325559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1407796</t>
+          <t>1405534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152593</t>
+          <t>152054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195855</t>
+          <t>197148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>281688</t>
+          <t>283626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337699</t>
+          <t>335754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443735</t>
+          <t>446343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>517273</t>
+          <t>516969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412897</t>
+          <t>411604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456159</t>
+          <t>456698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>394648</t>
+          <t>396593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>450659</t>
+          <t>448721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823826</t>
+          <t>824130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>897364</t>
+          <t>894756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>341302</t>
+          <t>340327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>405731</t>
+          <t>406490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367350</t>
+          <t>369986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441354</t>
+          <t>436400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238401</t>
+          <t>239739</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259275</t>
+          <t>259839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>658594</t>
+          <t>657835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>723023</t>
+          <t>723998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901167</t>
+          <t>906121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975171</t>
+          <t>972535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>876675</t>
+          <t>874362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>980787</t>
+          <t>980659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1154800</t>
+          <t>1157119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1271970</t>
+          <t>1270144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2056017</t>
+          <t>2055139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2216051</t>
+          <t>2215215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2350105</t>
+          <t>2350233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2454217</t>
+          <t>2456530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2213297</t>
+          <t>2215123</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2330467</t>
+          <t>2328148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4600108</t>
+          <t>4600944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4760142</t>
+          <t>4761020</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>172798</t>
+          <t>196335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150701</t>
+          <t>173455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194761</t>
+          <t>221406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>138144</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111115</t>
+          <t>121314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140402</t>
+          <t>155675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>297344</t>
+          <t>334479</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270124</t>
+          <t>307457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>324051</t>
+          <t>365898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>332414</t>
+          <t>354283</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310451</t>
+          <t>329212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354511</t>
+          <t>377163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>322920</t>
+          <t>350267</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307065</t>
+          <t>332736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336352</t>
+          <t>367097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>655335</t>
+          <t>704550</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628628</t>
+          <t>673131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682555</t>
+          <t>731572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>174339</t>
+          <t>189232</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153453</t>
+          <t>164492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>194822</t>
+          <t>208984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>142956</t>
+          <t>159028</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126255</t>
+          <t>142394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159179</t>
+          <t>175379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>317295</t>
+          <t>348260</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294288</t>
+          <t>321140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346434</t>
+          <t>379234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>277874</t>
+          <t>293980</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257391</t>
+          <t>274228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298760</t>
+          <t>318720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>238793</t>
+          <t>263250</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>246899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>255494</t>
+          <t>279884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>516666</t>
+          <t>557230</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487527</t>
+          <t>526256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>539673</t>
+          <t>584350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>164327</t>
+          <t>181742</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>161425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269612</t>
+          <t>202455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69177</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59050</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80147</t>
+          <t>89848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>233504</t>
+          <t>259234</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114661</t>
+          <t>234400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337698</t>
+          <t>280466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>503937</t>
+          <t>289870</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398652</t>
+          <t>269157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606961</t>
+          <t>310187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97734</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>97649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107861</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>601671</t>
+          <t>399875</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>497477</t>
+          <t>378643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>720514</t>
+          <t>424709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>371135</t>
+          <t>410101</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>337054</t>
+          <t>375805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>404689</t>
+          <t>445768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>252707</t>
+          <t>282508</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118993</t>
+          <t>258877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326914</t>
+          <t>310734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>623842</t>
+          <t>692610</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>437775</t>
+          <t>654072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>710019</t>
+          <t>736749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>663684</t>
+          <t>721742</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630130</t>
+          <t>686075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>697765</t>
+          <t>756038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>723849</t>
+          <t>577135</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649642</t>
+          <t>548909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>857563</t>
+          <t>600766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1387533</t>
+          <t>1298876</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301356</t>
+          <t>1254737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1573600</t>
+          <t>1337414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>152589</t>
+          <t>171253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133868</t>
+          <t>149766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173740</t>
+          <t>198753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>339448</t>
+          <t>378461</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>257419</t>
+          <t>356363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>390498</t>
+          <t>403064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>492037</t>
+          <t>549714</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394802</t>
+          <t>517498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>538433</t>
+          <t>586610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>322457</t>
+          <t>396711</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301306</t>
+          <t>369211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341178</t>
+          <t>418198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>499548</t>
+          <t>451666</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448498</t>
+          <t>427063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>581577</t>
+          <t>473764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>822004</t>
+          <t>848377</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775608</t>
+          <t>811481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>919239</t>
+          <t>880593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>73399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>315571</t>
+          <t>353892</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>290020</t>
+          <t>328400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341335</t>
+          <t>383777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>358105</t>
+          <t>404569</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>323408</t>
+          <t>371874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>389168</t>
+          <t>437929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>197973</t>
+          <t>186551</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177405</t>
+          <t>163829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213838</t>
+          <t>202479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>444853</t>
+          <t>489367</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>419089</t>
+          <t>459482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>470404</t>
+          <t>514859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>642826</t>
+          <t>675918</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>611763</t>
+          <t>642558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>677523</t>
+          <t>708613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1077723</t>
+          <t>1199340</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>841527</t>
+          <t>1140000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1181047</t>
+          <t>1258432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1244405</t>
+          <t>1389526</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1016340</t>
+          <t>1340316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1353526</t>
+          <t>1443553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2322128</t>
+          <t>2588866</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2019848</t>
+          <t>2509362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2490818</t>
+          <t>2669692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2298337</t>
+          <t>2243136</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2195013</t>
+          <t>2184044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2534533</t>
+          <t>2302476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2327697</t>
+          <t>2241690</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2218576</t>
+          <t>2187663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2555762</t>
+          <t>2290900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4626035</t>
+          <t>4484826</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4457345</t>
+          <t>4404000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4928315</t>
+          <t>4564330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
